--- a/Para excel/Control_Maquinas_Semanal_actualizado.xlsx
+++ b/Para excel/Control_Maquinas_Semanal_actualizado.xlsx
@@ -941,9 +941,15 @@
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+      <c r="N10" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
@@ -976,9 +982,15 @@
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
